--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_REAL MADRID.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_REAL MADRID.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA42"/>
+  <dimension ref="A1:BA44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>299.72</v>
+        <v>451.64</v>
       </c>
       <c r="C2" t="n">
-        <v>298.86</v>
+        <v>450.7399999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>115.1040621026568</v>
+        <v>118.4718462972002</v>
       </c>
       <c r="E2" t="n">
-        <v>105.0659171518437</v>
+        <v>110.041265474553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5363636363636364</v>
+        <v>0.5432692307692307</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1269035532994924</v>
+        <v>0.1181762732540409</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3154362416107382</v>
+        <v>0.3215859030837004</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1781818181818182</v>
+        <v>0.1971153846153846</v>
       </c>
       <c r="J2" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N2" t="n">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="O2" t="n">
-        <v>122</v>
+        <v>203</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4436363636363637</v>
+        <v>0.4879807692307692</v>
       </c>
       <c r="Q2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="R2" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2836363636363636</v>
+        <v>0.2355769230769231</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V2" t="n">
-        <v>0.02181818181818182</v>
+        <v>0.02403846153846154</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01454545454545455</v>
+        <v>0.04086538461538462</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AA2" t="n">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4145454545454546</v>
+        <v>0.4086538461538461</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8442622950819673</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3974358974358974</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.75</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.688524590163935</v>
+        <v>1.655172413793103</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.042372881355932</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.088888888888889</v>
+        <v>0.08450704225352113</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.042553191489362</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.782608695652174</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.840909090909091</v>
+        <v>1.967741935483871</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.25</v>
+        <v>6.709677419354839</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.090909090909092</v>
+        <v>8.67741935483871</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.92999999999999</v>
+        <v>75.27333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>74.71499999999999</v>
+        <v>75.12333333333332</v>
       </c>
       <c r="D3" t="n">
-        <v>115.1040621026568</v>
+        <v>118.4718462972002</v>
       </c>
       <c r="E3" t="n">
-        <v>105.0659171518437</v>
+        <v>110.041265474553</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5363636363636364</v>
+        <v>0.5432692307692308</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1269035532994924</v>
+        <v>0.1181762732540409</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3154362416107382</v>
+        <v>0.3215859030837004</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1781818181818182</v>
+        <v>0.1971153846153846</v>
       </c>
       <c r="J3" t="n">
-        <v>12.25</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>9.166666666666666</v>
+      </c>
+      <c r="N3" t="n">
+        <v>28</v>
+      </c>
+      <c r="O3" t="n">
+        <v>33.83333333333334</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.4879807692307693</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>16.33333333333333</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2355769230769231</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.02403846153846154</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.04086538461538462</v>
+      </c>
+      <c r="Z3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="O3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.4436363636363637</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="R3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.2836363636363636</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.02181818181818182</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.01454545454545455</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AA3" t="n">
-        <v>28.5</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4145454545454546</v>
+        <v>0.4086538461538461</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8442622950819673</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3974358974358974</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.75</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.688524590163935</v>
+        <v>1.655172413793103</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.042372881355932</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.088888888888889</v>
+        <v>0.08450704225352113</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.042553191489362</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.782608695652174</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.840909090909091</v>
+        <v>1.967741935483871</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.25</v>
+        <v>6.709677419354838</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.090909090909092</v>
+        <v>8.677419354838708</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>298</v>
+        <v>449.84</v>
       </c>
       <c r="C4" t="n">
-        <v>298.86</v>
+        <v>450.7399999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>105.0659171518437</v>
+        <v>110.041265474553</v>
       </c>
       <c r="E4" t="n">
-        <v>115.1040621026568</v>
+        <v>118.4718462972002</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4942084942084942</v>
+        <v>0.5256410256410257</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1335311572700297</v>
+        <v>0.1392593754903499</v>
       </c>
       <c r="H4" t="n">
-        <v>0.261744966442953</v>
+        <v>0.2752293577981652</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2239382239382239</v>
+        <v>0.2205128205128205</v>
       </c>
       <c r="J4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="N4" t="n">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="O4" t="n">
-        <v>119</v>
+        <v>194</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4594594594594595</v>
+        <v>0.4974358974358974</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="R4" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="T4" t="n">
         <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06563706563706563</v>
+        <v>0.05897435897435897</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="AA4" t="n">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3204633204633205</v>
+        <v>0.3230769230769231</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8403361344537815</v>
+        <v>0.8608247422680413</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3956043956043956</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3373493975903614</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.680672268907563</v>
+        <v>1.721649484536083</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>1.079136690647482</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.5681818181818182</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9743589743589743</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.777777777777778</v>
+        <v>3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.177777777777778</v>
+        <v>1.295774647887324</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.755555555555556</v>
+        <v>5.492957746478873</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.933333333333334</v>
+        <v>6.788732394366197</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.5</v>
+        <v>74.97333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>74.71499999999999</v>
+        <v>75.12333333333332</v>
       </c>
       <c r="D5" t="n">
-        <v>105.0659171518437</v>
+        <v>110.041265474553</v>
       </c>
       <c r="E5" t="n">
-        <v>115.1040621026568</v>
+        <v>118.4718462972002</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4942084942084942</v>
+        <v>0.5256410256410257</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1335311572700297</v>
+        <v>0.1392593754903499</v>
       </c>
       <c r="H5" t="n">
-        <v>0.261744966442953</v>
+        <v>0.2752293577981652</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2239382239382239</v>
+        <v>0.2205128205128205</v>
       </c>
       <c r="J5" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>10.5</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="O5" t="n">
-        <v>29.75</v>
+        <v>32.33333333333334</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4594594594594595</v>
+        <v>0.4974358974358974</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="R5" t="n">
-        <v>22.75</v>
+        <v>20</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="T5" t="n">
-        <v>1.25</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="U5" t="n">
-        <v>4.25</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06563706563706563</v>
+        <v>0.05897435897435898</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="X5" t="n">
-        <v>1.75</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.75</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3204633204633205</v>
+        <v>0.3230769230769231</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8403361344537815</v>
+        <v>0.8608247422680412</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3956043956043956</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3373493975903614</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.680672268907563</v>
+        <v>1.721649484536082</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>1.079136690647482</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.5681818181818182</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9743589743589743</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.777777777777778</v>
+        <v>3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.177777777777778</v>
+        <v>1.295774647887324</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.755555555555556</v>
+        <v>5.492957746478873</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.933333333333334</v>
+        <v>6.788732394366196</v>
       </c>
     </row>
     <row r="7">
@@ -1429,40 +1429,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31</v>
+      </c>
+      <c r="F8" t="n">
+        <v>17</v>
+      </c>
+      <c r="G8" t="n">
+        <v>33</v>
+      </c>
+      <c r="H8" t="n">
         <v>7</v>
       </c>
-      <c r="E8" t="n">
-        <v>18</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" t="n">
-        <v>21</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
         <v>5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
@@ -1477,139 +1477,139 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T8" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
         <v>5</v>
       </c>
-      <c r="X8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AG8" t="n">
         <v>0.2</v>
       </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AK8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AL8" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.421</v>
+        <v>0.464</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>171:21</t>
+          <t>136:32</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>43.64</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.526</v>
+        <v>0.617</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.54</v>
+        <v>0.629</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.031</v>
+        <v>1.222</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.046</v>
+        <v>0.028</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.103</v>
+        <v>0.109</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="AW8" t="n">
-        <v>22.5</v>
+        <v>36</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.118</v>
+        <v>0.236</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.031</v>
+        <v>0.062</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>#6 A. ABALDE</t>
+          <t>#1 D. KRAMER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1621,13 +1621,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1636,25 +1636,25 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1672,19 +1672,19 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -1699,33 +1699,33 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>120:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.583</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
@@ -1734,19 +1734,19 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -1755,926 +1755,926 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>#7 F. CAMPAZZO</t>
+          <t>#6 A. ABALDE</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>21</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="C10" t="n">
-        <v>65</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>16</v>
-      </c>
-      <c r="F10" t="n">
-        <v>14</v>
-      </c>
-      <c r="G10" t="n">
-        <v>29</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>18</v>
-      </c>
-      <c r="K10" t="n">
-        <v>12</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>11</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>9</v>
-      </c>
-      <c r="S10" t="n">
-        <v>14</v>
-      </c>
-      <c r="T10" t="n">
-        <v>77</v>
-      </c>
-      <c r="U10" t="n">
-        <v>6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>7</v>
-      </c>
-      <c r="X10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="AL10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>83:33</t>
+        </is>
+      </c>
+      <c r="AO10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV10" t="n">
         <v>10</v>
       </c>
-      <c r="Z10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>184:17</t>
-        </is>
-      </c>
-      <c r="AO10" t="n">
-        <v>55.52</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.171</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.571</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>6.429</v>
-      </c>
       <c r="AW10" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.139</v>
+        <v>0.12</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.012</v>
+        <v>0.051</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.171</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>#8 C. OKEKE</t>
+          <t>#7 F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" t="n">
+        <v>39</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32</v>
+      </c>
+      <c r="K11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
         <v>6</v>
       </c>
-      <c r="F11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" t="n">
-        <v>11</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>13</v>
+      </c>
+      <c r="R11" t="n">
+        <v>14</v>
+      </c>
+      <c r="S11" t="n">
+        <v>21</v>
+      </c>
+      <c r="T11" t="n">
+        <v>89</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="AB11" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
-        <v>9</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>34</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AC11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>151:09</t>
+        </is>
+      </c>
+      <c r="AO11" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.133</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="AW11" t="n">
         <v>6</v>
       </c>
-      <c r="Z11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>164:41</t>
-        </is>
-      </c>
-      <c r="AO11" t="n">
-        <v>18.88</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.165</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>21</v>
-      </c>
       <c r="AX11" t="n">
-        <v>0.053</v>
+        <v>0.241</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.059</v>
+        <v>0.021</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.033</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.034</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>#9 G. PROCIDA</t>
+          <t>#8 C. OKEKE</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>27</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>11</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>40</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>116:57</t>
+        </is>
+      </c>
+      <c r="AO12" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AU12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AO12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.073</v>
+        <v>0.105</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>#11 M. HEZONJA</t>
+          <t>#9 G. PROCIDA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" t="n">
-        <v>18</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="n">
-        <v>13</v>
-      </c>
-      <c r="J13" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="AO13" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
-        <v>5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>12</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>11</v>
-      </c>
-      <c r="T13" t="n">
-        <v>47</v>
-      </c>
-      <c r="U13" t="n">
-        <v>10</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>170:07</t>
-        </is>
-      </c>
-      <c r="AO13" t="n">
-        <v>59.72</v>
-      </c>
       <c r="AP13" t="n">
-        <v>0.402</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.46</v>
+        <v>1.25</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.72</v>
+        <v>2.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.218</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.244</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.231</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.154</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.385</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.162</v>
+        <v>0.317</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>#12 T. MALEDON</t>
+          <t>#11 M. HEZONJA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="n">
+        <v>19</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24</v>
+      </c>
+      <c r="K14" t="n">
+        <v>24</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>13</v>
+      </c>
+      <c r="R14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="n">
+        <v>22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>104</v>
+      </c>
+      <c r="U14" t="n">
         <v>3</v>
       </c>
-      <c r="G14" t="n">
-        <v>8</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="n">
-        <v>12</v>
-      </c>
-      <c r="J14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AB14" t="n">
         <v>3</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>13</v>
-      </c>
-      <c r="S14" t="n">
-        <v>14</v>
-      </c>
-      <c r="T14" t="n">
-        <v>48</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="AC14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2</v>
       </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>9</v>
-      </c>
-      <c r="X14" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AG14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>10</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>3</v>
-      </c>
       <c r="AL14" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.375</v>
+        <v>0.357</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>117:20</t>
+          <t>153:59</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>33.28</v>
+        <v>95</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.54</v>
+        <v>0.493</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.627</v>
+        <v>0.544</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.142</v>
+        <v>0.916</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.09</v>
+        <v>0.158</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.44</v>
+        <v>0.275</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.333</v>
+        <v>4.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>13.333</v>
+        <v>6.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.131</v>
+        <v>0.282</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.041</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.073</v>
+        <v>0.172</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.13</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>#14 G. DECK</t>
+          <t>#12 T. MALEDON</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
       </c>
       <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
         <v>2</v>
       </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T15" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="Z15" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.889</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB15" t="n">
         <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.571</v>
+        <v>0.364</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -2689,76 +2689,76 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>172:27</t>
+          <t>89:25</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>25.76</v>
+        <v>52.68</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.7</v>
+        <v>0.527</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.666</v>
+        <v>0.621</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.126</v>
+        <v>1.101</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.155</v>
+        <v>0.114</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.05</v>
+        <v>0.514</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>3.167</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>6.167</v>
       </c>
       <c r="AW15" t="n">
-        <v>6</v>
+        <v>9.333</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.012</v>
+        <v>0.024</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.05</v>
+        <v>0.148</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.035</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>#16 U. GARUBA</t>
+          <t>#13 I. ALMANSA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2767,73 +2767,73 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2864,111 +2864,111 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>143:31</t>
+          <t>00:19</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>29.76</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.766</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.378</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.101</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.333</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.667</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.096</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>#22 W. TAVARES</t>
+          <t>#14 G. DECK</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
+        <v>49</v>
+      </c>
+      <c r="D17" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2983,28 +2983,28 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3013,157 +3013,157 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>129:38</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>47.84</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>0.553</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1</v>
+        <v>0.572</v>
       </c>
       <c r="AR17" t="n">
-        <v>2</v>
+        <v>1.024</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.036</v>
+        <v>0.169</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.102</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>#23 S. LLULL</t>
+          <t>#16 U. GARUBA</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>43</v>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" t="n">
+        <v>28</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>15</v>
+      </c>
+      <c r="L18" t="n">
+        <v>10</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>65</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AB18" t="n">
         <v>6</v>
       </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3187,448 +3187,448 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>30:21</t>
+          <t>96:10</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>10.88</v>
+        <v>32.76</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.113</v>
+        <v>0.722</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.184</v>
+        <v>1.313</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.184</v>
+        <v>0.092</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.25</v>
+        <v>0.107</v>
       </c>
       <c r="AU18" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="AV18" t="n">
-        <v>4</v>
+        <v>9.333</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.165</v>
+        <v>0.156</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.035</v>
+        <v>0.11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>#24 A. FELIZ</t>
+          <t>#22 W. TAVARES</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
         <v>2</v>
       </c>
-      <c r="G19" t="n">
-        <v>13</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>9</v>
-      </c>
-      <c r="K19" t="n">
-        <v>11</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>37</v>
-      </c>
-      <c r="U19" t="n">
-        <v>8</v>
-      </c>
-      <c r="V19" t="n">
-        <v>7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>7</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>174:48</t>
-        </is>
-      </c>
-      <c r="AO19" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0.8120000000000001</v>
-      </c>
       <c r="AS19" t="n">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>10.75</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.107</v>
+        <v>0.164</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.068</v>
+        <v>0.396</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>#25 A. LEN</t>
+          <t>#23 S. LLULL</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
         <v>7</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>31:43</t>
+        </is>
+      </c>
+      <c r="AO20" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV20" t="n">
         <v>6</v>
       </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>10</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>11</v>
-      </c>
-      <c r="S20" t="n">
-        <v>6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>25</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>123:41</t>
-        </is>
-      </c>
-      <c r="AO20" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.667</v>
-      </c>
       <c r="AW20" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.051</v>
+        <v>0.215</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.043</v>
+        <v>0.033</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.008</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#24 A. FELIZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
+        <v>19</v>
+      </c>
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" t="n">
-        <v>3</v>
-      </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -3643,22 +3643,22 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>0.826</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3670,130 +3670,130 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>131:13</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>0.517</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>9.167</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>11.333</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#25 A. LEN</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -3808,22 +3808,22 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3847,216 +3847,216 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>73:42</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>13.64</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="L23" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.844</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.397</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>800:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>346.72</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.5679999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.992</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.127</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.178</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.841</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.090999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.148</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -4065,163 +4065,163 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>314</v>
+        <v>534</v>
       </c>
       <c r="D24" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="E24" t="n">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="G24" t="n">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="H24" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="I24" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="J24" t="n">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="K24" t="n">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="M24" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="N24" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="Q24" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="R24" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="S24" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="T24" t="n">
-        <v>374</v>
+        <v>654</v>
       </c>
       <c r="U24" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="Z24" t="n">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.84</v>
+        <v>0.828</v>
       </c>
       <c r="AB24" t="n">
         <v>36</v>
       </c>
       <c r="AC24" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.396</v>
+        <v>0.367</v>
       </c>
       <c r="AE24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI24" t="n">
         <v>17</v>
       </c>
-      <c r="AG24" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>0.286</v>
+        <v>0.471</v>
       </c>
       <c r="AK24" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AL24" t="n">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.337</v>
+        <v>0.353</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>800:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>337</v>
+        <v>524.64</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.494</v>
+        <v>0.543</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.538</v>
+        <v>0.577</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.018</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.134</v>
+        <v>0.118</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.224</v>
+        <v>0.197</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.178</v>
+        <v>1.968</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.756</v>
+        <v>6.71</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.933</v>
+        <v>8.677</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.052</v>
+        <v>0.064</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.137</v>
+        <v>0.145</v>
       </c>
       <c r="BA24" t="n">
         <v>0</v>
@@ -4230,295 +4230,295 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr"/>
-      <c r="BA25" t="inlineStr"/>
+          <t>Rival</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>496</v>
+      </c>
+      <c r="D25" t="n">
+        <v>130</v>
+      </c>
+      <c r="E25" t="n">
+        <v>251</v>
+      </c>
+      <c r="F25" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" t="n">
+        <v>139</v>
+      </c>
+      <c r="H25" t="n">
+        <v>86</v>
+      </c>
+      <c r="I25" t="n">
+        <v>111</v>
+      </c>
+      <c r="J25" t="n">
+        <v>92</v>
+      </c>
+      <c r="K25" t="n">
+        <v>154</v>
+      </c>
+      <c r="L25" t="n">
+        <v>60</v>
+      </c>
+      <c r="M25" t="n">
+        <v>31</v>
+      </c>
+      <c r="N25" t="n">
+        <v>41</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>67</v>
+      </c>
+      <c r="R25" t="n">
+        <v>106</v>
+      </c>
+      <c r="S25" t="n">
+        <v>131</v>
+      </c>
+      <c r="T25" t="n">
+        <v>593</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>167</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>194</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>126</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>1200:00</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>509.84</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>5.493</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>6.789</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#0 T. LYLES (Per Game)</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="G26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>57</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>42:50</t>
-        </is>
-      </c>
-      <c r="AO26" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.031</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0.054</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#6 A. ABALDE (Per Game)</t>
+          <t>#0 T. LYLES (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>1.75</v>
+        <v>14.333</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5</v>
+        <v>2.333</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>5.167</v>
       </c>
       <c r="F27" t="n">
-        <v>0.25</v>
+        <v>2.833</v>
       </c>
       <c r="G27" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="K27" t="n">
-        <v>0.75</v>
+        <v>4.333</v>
       </c>
       <c r="L27" t="n">
-        <v>0.25</v>
+        <v>1.333</v>
       </c>
       <c r="M27" t="n">
-        <v>0.25</v>
+        <v>0.833</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.5</v>
+        <v>0.167</v>
       </c>
       <c r="R27" t="n">
         <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="T27" t="n">
-        <v>-3</v>
+        <v>106</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -4527,187 +4527,187 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="AD27" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0.667</v>
       </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.25</v>
+        <v>2.167</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.5</v>
+        <v>4.667</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.167</v>
+        <v>0.464</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>30:02</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>3</v>
+        <v>11.733</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.35</v>
+        <v>0.617</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.35</v>
+        <v>0.629</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.583</v>
+        <v>1.222</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.167</v>
+        <v>0.028</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV27" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="AW27" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.046</v>
+        <v>0.236</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.062</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.027</v>
+        <v>0.21</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#7 F. CAMPAZZO (Per Game)</t>
+          <t>#1 D. KRAMER (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4728,316 +4728,316 @@
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.483</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>46:04</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>13.88</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.644</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.171</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.571</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.429</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#8 C. OKEKE (Per Game)</t>
+          <t>#6 A. ABALDE (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="T29" t="n">
+        <v>11</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AO29" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
         <v>1.5</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>34</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>41:10</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.165</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4</v>
-      </c>
       <c r="AV29" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.053</v>
+        <v>0.12</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.059</v>
+        <v>0.051</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.033</v>
+        <v>0.066</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.034</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#9 G. PROCIDA (Per Game)</t>
+          <t>#7 F. CAMPAZZO (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
+        <v>13</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>89</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.667</v>
       </c>
-      <c r="D30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>5</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5052,652 +5052,652 @@
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.333</v>
+        <v>2.667</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.333</v>
+        <v>6.333</v>
       </c>
       <c r="AM30" t="n">
-        <v>1</v>
+        <v>0.421</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>04:11</t>
+          <t>25:11</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>0.667</v>
+        <v>13.267</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.25</v>
+        <v>0.569</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.25</v>
+        <v>0.604</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.5</v>
+        <v>0.98</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.133</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>3.867</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.073</v>
+        <v>0.241</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#11 M. HEZONJA (Per Game)</t>
+          <t>#8 C. OKEKE (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>10.75</v>
+        <v>4.5</v>
       </c>
       <c r="D31" t="n">
-        <v>2.25</v>
+        <v>0.833</v>
       </c>
       <c r="E31" t="n">
-        <v>5.75</v>
+        <v>1.333</v>
       </c>
       <c r="F31" t="n">
-        <v>1.25</v>
+        <v>0.833</v>
       </c>
       <c r="G31" t="n">
-        <v>4.5</v>
+        <v>2.667</v>
       </c>
       <c r="H31" t="n">
-        <v>2.5</v>
+        <v>0.333</v>
       </c>
       <c r="I31" t="n">
-        <v>3.25</v>
+        <v>0.333</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>4.25</v>
+        <v>1.833</v>
       </c>
       <c r="L31" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="T31" t="n">
+        <v>40</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>0.5</v>
       </c>
-      <c r="M31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="AK31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AU31" t="n">
         <v>3</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T31" t="n">
-        <v>47</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>42:31</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.231</v>
-      </c>
       <c r="AV31" t="n">
-        <v>3.154</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.385</v>
+        <v>15</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.162</v>
+        <v>0.105</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.013</v>
+        <v>0.099</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.142</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#12 T. MALEDON (Per Game)</t>
+          <t>#9 G. PROCIDA (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>2.25</v>
+        <v>0.2</v>
       </c>
       <c r="E32" t="n">
-        <v>4.25</v>
+        <v>0.2</v>
       </c>
       <c r="F32" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="H32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="U32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AC32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="AO32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR32" t="n">
         <v>2.5</v>
       </c>
-      <c r="AD32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>29:20</t>
-        </is>
-      </c>
-      <c r="AO32" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.142</v>
-      </c>
       <c r="AS32" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>8.333</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>13.333</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.131</v>
+        <v>0.317</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#14 G. DECK (Per Game)</t>
+          <t>#11 M. HEZONJA (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="J33" t="n">
         <v>4</v>
       </c>
-      <c r="C33" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="K33" t="n">
         <v>4</v>
       </c>
-      <c r="F33" t="n">
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="T33" t="n">
+        <v>104</v>
+      </c>
+      <c r="U33" t="n">
         <v>0.5</v>
       </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AB33" t="n">
         <v>0.5</v>
       </c>
-      <c r="M33" t="n">
+      <c r="AC33" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.5</v>
       </c>
-      <c r="N33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T33" t="n">
-        <v>30</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.5</v>
+        <v>1.667</v>
       </c>
       <c r="AL33" t="n">
-        <v>1</v>
+        <v>4.667</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.5</v>
+        <v>0.357</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>43:06</t>
+          <t>25:39</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.44</v>
+        <v>15.833</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.7</v>
+        <v>0.493</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.666</v>
+        <v>0.544</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.126</v>
+        <v>0.916</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.155</v>
+        <v>0.158</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.05</v>
+        <v>0.275</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.282</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.012</v>
+        <v>0.041</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.05</v>
+        <v>0.172</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.035</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#16 U. GARUBA (Per Game)</t>
+          <t>#12 T. MALEDON (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>10.25</v>
+        <v>9.667</v>
       </c>
       <c r="D34" t="n">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>6.25</v>
+        <v>4.167</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>0.75</v>
+        <v>3.167</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>3.667</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>3.167</v>
       </c>
       <c r="K34" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>0.333</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0.167</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>0.333</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>2.667</v>
       </c>
       <c r="S34" t="n">
-        <v>0.75</v>
+        <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="U34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.889</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.5</v>
+        <v>0.667</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.5</v>
+        <v>1.833</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.6</v>
+        <v>0.364</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5718,76 +5718,76 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>35:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>7.44</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.76</v>
+        <v>0.527</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.766</v>
+        <v>0.621</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.378</v>
+        <v>1.101</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.101</v>
+        <v>0.114</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.12</v>
+        <v>0.514</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.333</v>
+        <v>3.167</v>
       </c>
       <c r="AV34" t="n">
-        <v>8.333</v>
+        <v>6.167</v>
       </c>
       <c r="AW34" t="n">
-        <v>9.667</v>
+        <v>9.333</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.096</v>
+        <v>0.27</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.075</v>
+        <v>0.024</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.075</v>
+        <v>0.148</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.037</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#22 W. TAVARES (Per Game)</t>
+          <t>#13 I. ALMANSA (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -5832,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -5847,13 +5847,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -5893,20 +5893,20 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>00:09</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
         <v>0</v>
@@ -5924,13 +5924,13 @@
         <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
         <v>0</v>
@@ -5939,260 +5939,260 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#23 S. LLULL (Per Game)</t>
+          <t>#14 G. DECK (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="M36" t="n">
         <v>0.5</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="N36" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="T36" t="n">
+        <v>54</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AD36" t="n">
         <v>0.5</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L36" t="n">
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AM36" t="n">
         <v>0.25</v>
       </c>
-      <c r="M36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T36" t="n">
-        <v>-4</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>2.72</v>
+        <v>7.973</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.553</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.113</v>
+        <v>0.572</v>
       </c>
       <c r="AR36" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AT36" t="n">
         <v>0.184</v>
       </c>
-      <c r="AS36" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AU36" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AV36" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.165</v>
+        <v>0.169</v>
       </c>
       <c r="AY36" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="BA36" t="n">
         <v>0.035</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0.031</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#24 A. FELIZ (Per Game)</t>
+          <t>#16 U. GARUBA (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D37" t="n">
         <v>4</v>
       </c>
-      <c r="C37" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
         <v>3</v>
       </c>
-      <c r="E37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2.75</v>
-      </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="N37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="T37" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.917</v>
+        <v>0.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.333</v>
+        <v>0.545</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6204,131 +6204,131 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>43:42</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>10.16</v>
+        <v>6.552</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.441</v>
+        <v>0.714</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.45</v>
+        <v>0.722</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.313</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.098</v>
+        <v>0.092</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.25</v>
+        <v>1.667</v>
       </c>
       <c r="AV37" t="n">
-        <v>8.5</v>
+        <v>9.333</v>
       </c>
       <c r="AW37" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.107</v>
+        <v>0.156</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.037</v>
+        <v>0.11</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.068</v>
+        <v>0.172</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.08</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#25 A. LEN (Per Game)</t>
+          <t>#22 W. TAVARES (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
         <v>3</v>
       </c>
-      <c r="D38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>25</v>
-      </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
@@ -6342,22 +6342,22 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6381,97 +6381,97 @@
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
         <v>0</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>30:55</t>
+          <t>02:47</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>3.41</v>
+        <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.5639999999999999</v>
+        <v>1</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.051</v>
+        <v>0.164</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.396</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#23 S. LLULL (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="K39" t="n">
-        <v>2.25</v>
+        <v>0.333</v>
       </c>
       <c r="L39" t="n">
-        <v>0.75</v>
+        <v>0.167</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -6480,19 +6480,19 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -6507,19 +6507,19 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -6534,130 +6534,130 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM39" t="n">
         <v>0</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:17</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>0.336</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>0.215</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#24 A. FELIZ (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>10.167</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>3.167</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>5.667</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>3.167</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T40" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -6672,22 +6672,22 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>3.167</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.833</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>0.826</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -6699,395 +6699,725 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>3.333</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>10.827</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>0.517</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>9.167</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>11.333</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>TOTAL (Per Game)</t>
+          <t>#25 A. LEN (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>21.5</v>
+        <v>0.75</v>
       </c>
       <c r="E41" t="n">
-        <v>39.25</v>
+        <v>1.75</v>
       </c>
       <c r="F41" t="n">
-        <v>10.25</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>29.5</v>
+        <v>0.25</v>
       </c>
       <c r="H41" t="n">
-        <v>12.25</v>
+        <v>1.5</v>
       </c>
       <c r="I41" t="n">
-        <v>15.75</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
-        <v>20.25</v>
+        <v>0.25</v>
       </c>
       <c r="K41" t="n">
-        <v>27.5</v>
+        <v>2.5</v>
       </c>
       <c r="L41" t="n">
-        <v>11.75</v>
+        <v>1.25</v>
       </c>
       <c r="M41" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>11</v>
+        <v>0.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>10</v>
+        <v>0.75</v>
       </c>
       <c r="R41" t="n">
-        <v>18.75</v>
+        <v>2.75</v>
       </c>
       <c r="S41" t="n">
-        <v>17.75</v>
+        <v>1.5</v>
       </c>
       <c r="T41" t="n">
-        <v>429</v>
+        <v>25</v>
       </c>
       <c r="U41" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>10.25</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>25.75</v>
+        <v>1.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>30.5</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.844</v>
+        <v>0.778</v>
       </c>
       <c r="AB41" t="n">
-        <v>7.75</v>
+        <v>0.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>19.5</v>
+        <v>1</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.397</v>
+        <v>0.5</v>
       </c>
       <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
         <v>0.25</v>
       </c>
-      <c r="AF41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AH41" t="n">
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AO41" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AT41" t="n">
         <v>0.75</v>
       </c>
-      <c r="AI41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AM41" t="n">
+      <c r="AU41" t="n">
         <v>0.333</v>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO41" t="n">
-        <v>86.68000000000001</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>1.841</v>
-      </c>
       <c r="AV41" t="n">
-        <v>6.25</v>
+        <v>2.667</v>
       </c>
       <c r="AW41" t="n">
-        <v>8.090999999999999</v>
+        <v>3</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.2</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.063</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
+          <t>Equip (Per Game)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (Per Game)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" t="n">
+        <v>89</v>
+      </c>
+      <c r="D43" t="n">
+        <v>20.667</v>
+      </c>
+      <c r="E43" t="n">
+        <v>38.167</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11.333</v>
+      </c>
+      <c r="G43" t="n">
+        <v>31.167</v>
+      </c>
+      <c r="H43" t="n">
+        <v>13.667</v>
+      </c>
+      <c r="I43" t="n">
+        <v>17.667</v>
+      </c>
+      <c r="J43" t="n">
+        <v>20.333</v>
+      </c>
+      <c r="K43" t="n">
+        <v>26.333</v>
+      </c>
+      <c r="L43" t="n">
+        <v>12.167</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6.833</v>
+      </c>
+      <c r="N43" t="n">
+        <v>6.833</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>10.333</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>9.167</v>
+      </c>
+      <c r="R43" t="n">
+        <v>19.833</v>
+      </c>
+      <c r="S43" t="n">
+        <v>19</v>
+      </c>
+      <c r="T43" t="n">
+        <v>654</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>33.833</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>16.333</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>28.333</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>200:00</t>
+        </is>
+      </c>
+      <c r="AO43" t="n">
+        <v>87.44</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>8.677</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
           <t>Rival (Per Game)</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>4</v>
-      </c>
-      <c r="C42" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="D42" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="E42" t="n">
-        <v>42.25</v>
-      </c>
-      <c r="F42" t="n">
+      <c r="B44" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" t="n">
+        <v>82.667</v>
+      </c>
+      <c r="D44" t="n">
+        <v>21.667</v>
+      </c>
+      <c r="E44" t="n">
+        <v>41.833</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="G44" t="n">
+        <v>23.167</v>
+      </c>
+      <c r="H44" t="n">
+        <v>14.333</v>
+      </c>
+      <c r="I44" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>15.333</v>
+      </c>
+      <c r="K44" t="n">
+        <v>25.667</v>
+      </c>
+      <c r="L44" t="n">
+        <v>10</v>
+      </c>
+      <c r="M44" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="N44" t="n">
+        <v>6.833</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>11.833</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>11.167</v>
+      </c>
+      <c r="R44" t="n">
+        <v>17.667</v>
+      </c>
+      <c r="S44" t="n">
+        <v>21.833</v>
+      </c>
+      <c r="T44" t="n">
+        <v>593</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>27.833</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>32.333</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AK44" t="n">
         <v>7.5</v>
       </c>
-      <c r="G42" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H42" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I42" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="J42" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="K42" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="L42" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="M42" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="N42" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="S42" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="T42" t="n">
-        <v>374</v>
-      </c>
-      <c r="U42" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="V42" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>12</v>
-      </c>
-      <c r="X42" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="AN42" t="inlineStr">
+      <c r="AL44" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AN44" t="inlineStr">
         <is>
           <t>200:00</t>
         </is>
       </c>
-      <c r="AO42" t="n">
-        <v>84.25</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0.9320000000000001</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>1.178</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>5.756</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>6.933</v>
-      </c>
-      <c r="AX42" t="n">
+      <c r="AO44" t="n">
+        <v>84.973</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>5.493</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>6.789</v>
+      </c>
+      <c r="AX44" t="n">
         <v>0.194</v>
       </c>
-      <c r="AY42" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="BA42" t="n">
+      <c r="AY44" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="BA44" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_REAL MADRID.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_REAL MADRID.xlsx
@@ -671,13 +671,13 @@
         <v>0.1971153846153846</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M2" t="n">
         <v>55</v>
@@ -752,13 +752,13 @@
         <v>1.090909090909091</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.08450704225352113</v>
+        <v>0.9295774647887324</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.763157894736842</v>
       </c>
       <c r="AN2" t="n">
         <v>1.967741935483871</v>
@@ -801,13 +801,13 @@
         <v>0.1971153846153846</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="M3" t="n">
         <v>9.166666666666666</v>
@@ -882,13 +882,13 @@
         <v>1.090909090909091</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.08450704225352113</v>
+        <v>0.9295774647887324</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.763157894736842</v>
       </c>
       <c r="AN3" t="n">
         <v>1.967741935483871</v>
@@ -931,13 +931,13 @@
         <v>0.2205128205128205</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="M4" t="n">
         <v>67</v>
@@ -1012,13 +1012,13 @@
         <v>1.079136690647482</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="AM4" t="n">
-        <v>3</v>
+        <v>1.609756097560976</v>
       </c>
       <c r="AN4" t="n">
         <v>1.295774647887324</v>
@@ -1061,13 +1061,13 @@
         <v>0.2205128205128205</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
         <v>11.16666666666667</v>
@@ -1142,13 +1142,13 @@
         <v>1.079136690647482</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.9833333333333334</v>
       </c>
       <c r="AM5" t="n">
-        <v>3</v>
+        <v>1.609756097560976</v>
       </c>
       <c r="AN5" t="n">
         <v>1.295774647887324</v>
@@ -1486,16 +1486,16 @@
         <v>106</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
         <v>16</v>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1981,16 +1981,16 @@
         <v>89</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="n">
         <v>16</v>
@@ -2146,10 +2146,10 @@
         <v>40</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2476,16 +2476,16 @@
         <v>104</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="n">
         <v>34</v>
@@ -2641,16 +2641,16 @@
         <v>70</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y15" t="n">
         <v>27</v>
@@ -2971,16 +2971,16 @@
         <v>54</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
         <v>21</v>
@@ -3136,16 +3136,16 @@
         <v>65</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
         <v>17</v>
@@ -3631,16 +3631,16 @@
         <v>72</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y21" t="n">
         <v>19</v>
@@ -4126,16 +4126,16 @@
         <v>654</v>
       </c>
       <c r="U24" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y24" t="n">
         <v>168</v>
@@ -4291,16 +4291,16 @@
         <v>593</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="Y25" t="n">
         <v>167</v>
@@ -4515,16 +4515,16 @@
         <v>106</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="Y27" t="n">
         <v>2.667</v>
@@ -4848,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -5010,16 +5010,16 @@
         <v>89</v>
       </c>
       <c r="U30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="Y30" t="n">
         <v>2.667</v>
@@ -5175,10 +5175,10 @@
         <v>40</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5346,10 +5346,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -5505,16 +5505,16 @@
         <v>104</v>
       </c>
       <c r="U33" t="n">
-        <v>0.5</v>
+        <v>2.333</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
         <v>5.667</v>
@@ -5670,16 +5670,16 @@
         <v>70</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.167</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="Y34" t="n">
         <v>4.5</v>
@@ -6000,16 +6000,16 @@
         <v>54</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y36" t="n">
         <v>3.5</v>
@@ -6165,16 +6165,16 @@
         <v>65</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Y37" t="n">
         <v>3.4</v>
@@ -6660,16 +6660,16 @@
         <v>72</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="Y40" t="n">
         <v>3.167</v>
@@ -7155,16 +7155,16 @@
         <v>654</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>11.167</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>11.167</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>6.333</v>
       </c>
       <c r="Y43" t="n">
         <v>28</v>
@@ -7320,16 +7320,16 @@
         <v>593</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>6.667</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>9.833</v>
       </c>
       <c r="W44" t="n">
-        <v>0.5</v>
+        <v>11</v>
       </c>
       <c r="X44" t="n">
-        <v>0.167</v>
+        <v>6.833</v>
       </c>
       <c r="Y44" t="n">
         <v>27.833</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_REAL MADRID.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_REAL MADRID.xlsx
@@ -683,13 +683,13 @@
         <v>55</v>
       </c>
       <c r="N2" t="n">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="O2" t="n">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4879807692307692</v>
+        <v>0.2908653846153846</v>
       </c>
       <c r="Q2" t="n">
         <v>36</v>
@@ -710,25 +710,25 @@
         <v>0.02403846153846154</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04086538461538462</v>
+        <v>0.05288461538461538</v>
       </c>
       <c r="Z2" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="AA2" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4086538461538461</v>
+        <v>0.3966346153846154</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.7107438016528925</v>
       </c>
       <c r="AD2" t="n">
         <v>0.3673469387755102</v>
@@ -737,13 +737,13 @@
         <v>0.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.655172413793103</v>
+        <v>1.421487603305785</v>
       </c>
       <c r="AI2" t="n">
         <v>0.4</v>
@@ -813,13 +813,13 @@
         <v>9.166666666666666</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="O3" t="n">
-        <v>33.83333333333334</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4879807692307693</v>
+        <v>0.2908653846153846</v>
       </c>
       <c r="Q3" t="n">
         <v>6</v>
@@ -840,25 +840,25 @@
         <v>0.02403846153846154</v>
       </c>
       <c r="W3" t="n">
-        <v>1.333333333333333</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="X3" t="n">
-        <v>2.833333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04086538461538462</v>
+        <v>0.05288461538461538</v>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>28.33333333333333</v>
+        <v>27.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4086538461538461</v>
+        <v>0.3966346153846154</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.7107438016528925</v>
       </c>
       <c r="AD3" t="n">
         <v>0.3673469387755102</v>
@@ -867,13 +867,13 @@
         <v>0.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.655172413793103</v>
+        <v>1.421487603305785</v>
       </c>
       <c r="AI3" t="n">
         <v>0.4</v>
@@ -943,13 +943,13 @@
         <v>67</v>
       </c>
       <c r="N4" t="n">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="O4" t="n">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4974358974358974</v>
+        <v>0.2769230769230769</v>
       </c>
       <c r="Q4" t="n">
         <v>44</v>
@@ -970,25 +970,25 @@
         <v>0.05897435897435897</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03846153846153846</v>
       </c>
       <c r="Z4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3230769230769231</v>
+        <v>0.3179487179487179</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8608247422680413</v>
+        <v>0.75</v>
       </c>
       <c r="AD4" t="n">
         <v>0.3666666666666666</v>
@@ -997,13 +997,13 @@
         <v>0.2173913043478261</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.721649484536083</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
         <v>0.4347826086956522</v>
@@ -1073,13 +1073,13 @@
         <v>11.16666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>27.83333333333333</v>
+        <v>13.5</v>
       </c>
       <c r="O5" t="n">
-        <v>32.33333333333334</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4974358974358974</v>
+        <v>0.2769230769230769</v>
       </c>
       <c r="Q5" t="n">
         <v>7.333333333333333</v>
@@ -1100,25 +1100,25 @@
         <v>0.05897435897435898</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>2.166666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03846153846153846</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="AA5" t="n">
-        <v>21</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3230769230769231</v>
+        <v>0.317948717948718</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8608247422680412</v>
+        <v>0.75</v>
       </c>
       <c r="AD5" t="n">
         <v>0.3666666666666666</v>
@@ -1127,13 +1127,13 @@
         <v>0.2173913043478261</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3548387096774193</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.721649484536082</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
         <v>0.4347826086956522</v>
@@ -1498,13 +1498,13 @@
         <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.889</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB8" t="n">
         <v>4</v>
@@ -1525,22 +1525,22 @@
         <v>0.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="AK8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.464</v>
+        <v>0.444</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1855,22 +1855,22 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK10" t="n">
         <v>3</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AL10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM10" t="n">
         <v>0.333</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.364</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.762</v>
+        <v>0.444</v>
       </c>
       <c r="AB11" t="n">
         <v>5</v>
@@ -2158,13 +2158,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z12" t="n">
         <v>7</v>
       </c>
-      <c r="Z12" t="n">
-        <v>9</v>
-      </c>
       <c r="AA12" t="n">
-        <v>0.778</v>
+        <v>0.714</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2488,13 +2488,13 @@
         <v>6</v>
       </c>
       <c r="Y14" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="Z14" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.85</v>
+        <v>0.714</v>
       </c>
       <c r="AB14" t="n">
         <v>3</v>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -2527,10 +2527,10 @@
         <v>10</v>
       </c>
       <c r="AL14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.357</v>
+        <v>0.37</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         <v>10</v>
       </c>
       <c r="Y15" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="AB15" t="n">
         <v>4</v>
@@ -2983,13 +2983,13 @@
         <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.84</v>
+        <v>0.778</v>
       </c>
       <c r="AB17" t="n">
         <v>4</v>
@@ -3148,13 +3148,13 @@
         <v>2</v>
       </c>
       <c r="Y18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z18" t="n">
         <v>17</v>
       </c>
-      <c r="Z18" t="n">
-        <v>20</v>
-      </c>
       <c r="AA18" t="n">
-        <v>0.85</v>
+        <v>0.824</v>
       </c>
       <c r="AB18" t="n">
         <v>6</v>
@@ -3478,13 +3478,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3643,13 +3643,13 @@
         <v>7</v>
       </c>
       <c r="Y21" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.826</v>
+        <v>0.778</v>
       </c>
       <c r="AB21" t="n">
         <v>5</v>
@@ -3670,22 +3670,22 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.25</v>
+        <v>0.211</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -3808,13 +3808,13 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.778</v>
+        <v>0.333</v>
       </c>
       <c r="AB22" t="n">
         <v>2</v>
@@ -4138,13 +4138,13 @@
         <v>38</v>
       </c>
       <c r="Y24" t="n">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="Z24" t="n">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.828</v>
+        <v>0.711</v>
       </c>
       <c r="AB24" t="n">
         <v>36</v>
@@ -4165,22 +4165,22 @@
         <v>0.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI24" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.471</v>
+        <v>0.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="AL24" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.353</v>
+        <v>0.345</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -4303,13 +4303,13 @@
         <v>41</v>
       </c>
       <c r="Y25" t="n">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="Z25" t="n">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.861</v>
+        <v>0.75</v>
       </c>
       <c r="AB25" t="n">
         <v>44</v>
@@ -4330,22 +4330,22 @@
         <v>0.217</v>
       </c>
       <c r="AH25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="AK25" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AL25" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0.833</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.667</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>3</v>
+        <v>1.833</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.889</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB27" t="n">
         <v>0.667</v>
@@ -4554,22 +4554,22 @@
         <v>0.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="AI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>0.833</v>
       </c>
-      <c r="AJ27" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AK27" t="n">
-        <v>2.167</v>
+        <v>2</v>
       </c>
       <c r="AL27" t="n">
-        <v>4.667</v>
+        <v>4.5</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.464</v>
+        <v>0.444</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
@@ -4884,22 +4884,22 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="AI29" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK29" t="n">
         <v>0.5</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AL29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM29" t="n">
         <v>0.333</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.364</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5022,13 +5022,13 @@
         <v>0.667</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.667</v>
+        <v>0.667</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.762</v>
+        <v>0.444</v>
       </c>
       <c r="AB30" t="n">
         <v>0.833</v>
@@ -5187,13 +5187,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z31" t="n">
         <v>1.167</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA31" t="n">
-        <v>0.778</v>
+        <v>0.714</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -5517,13 +5517,13 @@
         <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.667</v>
+        <v>2.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.667</v>
+        <v>3.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.85</v>
+        <v>0.714</v>
       </c>
       <c r="AB33" t="n">
         <v>0.5</v>
@@ -5547,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
@@ -5556,10 +5556,10 @@
         <v>1.667</v>
       </c>
       <c r="AL33" t="n">
-        <v>4.667</v>
+        <v>4.5</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.357</v>
+        <v>0.37</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -5682,13 +5682,13 @@
         <v>1.667</v>
       </c>
       <c r="Y34" t="n">
-        <v>4.5</v>
+        <v>1.333</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.5</v>
+        <v>2.333</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="AB34" t="n">
         <v>0.667</v>
@@ -6012,13 +6012,13 @@
         <v>0.333</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.5</v>
+        <v>2.333</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.167</v>
+        <v>3</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.84</v>
+        <v>0.778</v>
       </c>
       <c r="AB36" t="n">
         <v>0.667</v>
@@ -6177,13 +6177,13 @@
         <v>0.4</v>
       </c>
       <c r="Y37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Z37" t="n">
         <v>3.4</v>
       </c>
-      <c r="Z37" t="n">
-        <v>4</v>
-      </c>
       <c r="AA37" t="n">
-        <v>0.85</v>
+        <v>0.824</v>
       </c>
       <c r="AB37" t="n">
         <v>1.2</v>
@@ -6507,13 +6507,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>1.167</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.167</v>
+        <v>2.333</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.833</v>
+        <v>3</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.826</v>
+        <v>0.778</v>
       </c>
       <c r="AB40" t="n">
         <v>0.833</v>
@@ -6699,22 +6699,22 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="AJ40" t="n">
         <v>1</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="AL40" t="n">
-        <v>3.333</v>
+        <v>3.167</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.25</v>
+        <v>0.211</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
@@ -6837,13 +6837,13 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.778</v>
+        <v>0.333</v>
       </c>
       <c r="AB41" t="n">
         <v>0.5</v>
@@ -7167,13 +7167,13 @@
         <v>6.333</v>
       </c>
       <c r="Y43" t="n">
-        <v>28</v>
+        <v>14.333</v>
       </c>
       <c r="Z43" t="n">
-        <v>33.833</v>
+        <v>20.167</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.828</v>
+        <v>0.711</v>
       </c>
       <c r="AB43" t="n">
         <v>6</v>
@@ -7194,22 +7194,22 @@
         <v>0.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.333</v>
+        <v>1.833</v>
       </c>
       <c r="AI43" t="n">
-        <v>2.833</v>
+        <v>3.667</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.471</v>
+        <v>0.5</v>
       </c>
       <c r="AK43" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AL43" t="n">
-        <v>28.333</v>
+        <v>27.5</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.353</v>
+        <v>0.345</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
@@ -7332,13 +7332,13 @@
         <v>6.833</v>
       </c>
       <c r="Y44" t="n">
-        <v>27.833</v>
+        <v>13.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>32.333</v>
+        <v>18</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.861</v>
+        <v>0.75</v>
       </c>
       <c r="AB44" t="n">
         <v>7.333</v>
@@ -7359,22 +7359,22 @@
         <v>0.217</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.167</v>
+        <v>2.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="AK44" t="n">
-        <v>7.5</v>
+        <v>7.333</v>
       </c>
       <c r="AL44" t="n">
-        <v>21</v>
+        <v>20.667</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
